--- a/EKG_Kalite_Yönetim_Sistemi/11_Bakım, Yedek Parça ve Takımlar/01_MAI1 - Bakım Planı ve Gerçekleşme/EKG-BAK-FRM-01_ekipman_bazli_bakim_gorev_foyleri.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/11_Bakım, Yedek Parça ve Takımlar/01_MAI1 - Bakım Planı ve Gerçekleşme/EKG-BAK-FRM-01_ekipman_bazli_bakim_gorev_foyleri.xlsx
@@ -1006,7 +1006,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-BAK-FRM-01&amp;C&amp;"Arial,Regular"&amp;11Ekipman Bazlı Bakım Görev Föyleri</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 23.09.2026
+Revizyon nedeni: Dört görev föyü gerçek iş adımları korunarak güvenli fonksiyon doğrulama, sonuç ve teslim kaydına indirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1198,7 +1199,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-BAK-FRM-01&amp;C&amp;"Arial,Regular"&amp;11Ekipman Bazlı Bakım Görev Föyleri</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 23.09.2026
+Revizyon nedeni: Dört görev föyü gerçek iş adımları korunarak güvenli fonksiyon doğrulama, sonuç ve teslim kaydına indirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1390,7 +1392,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-BAK-FRM-01&amp;C&amp;"Arial,Regular"&amp;11Ekipman Bazlı Bakım Görev Föyleri</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 23.09.2026
+Revizyon nedeni: Dört görev föyü gerçek iş adımları korunarak güvenli fonksiyon doğrulama, sonuç ve teslim kaydına indirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1582,7 +1585,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-BAK-FRM-01&amp;C&amp;"Arial,Regular"&amp;11Ekipman Bazlı Bakım Görev Föyleri</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 23.09.2026
+Revizyon nedeni: Dört görev föyü gerçek iş adımları korunarak güvenli fonksiyon doğrulama, sonuç ve teslim kaydına indirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>